--- a/it_forms/012_it_system_access_offboarding_form--it_forms.xlsx
+++ b/it_forms/012_it_system_access_offboarding_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,8 +1033,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'it'}</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'IT'}</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'finance'}</t>
+          <t>finance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Finance'}</t>
+          <t>Finance</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'access_to_email'}</t>
+          <t>access_to_email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Access to email'}</t>
+          <t>Access to email</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'access_to_network'}</t>
+          <t>access_to_network</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Access to network'}</t>
+          <t>Access to network</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'access_to_phone'}</t>
+          <t>access_to_phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Access to phone'}</t>
+          <t>Access to phone</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'access_to_shared_files'}</t>
+          <t>access_to_shared_files</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Access to shared files'}</t>
+          <t>Access to shared files</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'access_to_system_resources'}</t>
+          <t>access_to_system_resources</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Access to system resources'}</t>
+          <t>Access to system resources</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'access_to_system_admin_tools'}</t>
+          <t>access_to_system_admin_tools</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Access to system admin tools'}</t>
+          <t>Access to system admin tools</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'access_to_company_database'}</t>
+          <t>access_to_company_database</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Access to company database'}</t>
+          <t>Access to company database</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'access_to_user_profiles'}</t>
+          <t>access_to_user_profiles</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Access to user profiles'}</t>
+          <t>Access to user profiles</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'access_to_system_backups'}</t>
+          <t>access_to_system_backups</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Access to system backups'}</t>
+          <t>Access to system backups</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'access_to_security_logs'}</t>
+          <t>access_to_security_logs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Access to security logs'}</t>
+          <t>Access to security logs</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'access_to_system_configurations'}</t>
+          <t>access_to_system_configurations</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Access to system configurations'}</t>
+          <t>Access to system configurations</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'access_to_system_updates'}</t>
+          <t>access_to_system_updates</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Access to system updates'}</t>
+          <t>Access to system updates</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'access_to_all_systems'}</t>
+          <t>access_to_all_systems</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Access to all systems'}</t>
+          <t>Access to all systems</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1385,12 +1385,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'deleted'}</t>
+          <t>deleted</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Deleted'}</t>
+          <t>Deleted</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'blocked'}</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Blocked'}</t>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'locked'}</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Locked'}</t>
+          <t>Locked</t>
         </is>
       </c>
     </row>
@@ -1436,12 +1436,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'suspend'}</t>
+          <t>suspend</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Suspend'}</t>
+          <t>Suspend</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1470,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1487,12 +1487,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'network'}</t>
+          <t>network</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Network'}</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'system_resources'}</t>
+          <t>system_resources</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'System Resources'}</t>
+          <t>System Resources</t>
         </is>
       </c>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'system_admin_tools'}</t>
+          <t>system_admin_tools</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'System Admin Tools'}</t>
+          <t>System Admin Tools</t>
         </is>
       </c>
     </row>
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'company_database'}</t>
+          <t>company_database</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Company Database'}</t>
+          <t>Company Database</t>
         </is>
       </c>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'user_profiles'}</t>
+          <t>user_profiles</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'User Profiles'}</t>
+          <t>User Profiles</t>
         </is>
       </c>
     </row>
@@ -1589,12 +1589,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'system_backups'}</t>
+          <t>system_backups</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'System Backups'}</t>
+          <t>System Backups</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'security_logs'}</t>
+          <t>security_logs</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Security Logs'}</t>
+          <t>Security Logs</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'system_configurations'}</t>
+          <t>system_configurations</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'System Configurations'}</t>
+          <t>System Configurations</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'system_updates'}</t>
+          <t>system_updates</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'System Updates'}</t>
+          <t>System Updates</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'all_systems'}</t>
+          <t>all_systems</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'All Systems'}</t>
+          <t>All Systems</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'access_to_email'}</t>
+          <t>access_to_email</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Access to email'}</t>
+          <t>Access to email</t>
         </is>
       </c>
     </row>
@@ -1691,12 +1691,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'access_to_network'}</t>
+          <t>access_to_network</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Access to network'}</t>
+          <t>Access to network</t>
         </is>
       </c>
     </row>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'access_to_phone'}</t>
+          <t>access_to_phone</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Access to phone'}</t>
+          <t>Access to phone</t>
         </is>
       </c>
     </row>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'access_to_shared_files'}</t>
+          <t>access_to_shared_files</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Access to shared files'}</t>
+          <t>Access to shared files</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1742,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'access_to_system_resources'}</t>
+          <t>access_to_system_resources</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Access to system resources'}</t>
+          <t>Access to system resources</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'access_to_system_admin_tools'}</t>
+          <t>access_to_system_admin_tools</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Access to system admin tools'}</t>
+          <t>Access to system admin tools</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'access_to_company_database'}</t>
+          <t>access_to_company_database</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Access to company database'}</t>
+          <t>Access to company database</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'access_to_user_profiles'}</t>
+          <t>access_to_user_profiles</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Access to user profiles'}</t>
+          <t>Access to user profiles</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'access_to_system_backups'}</t>
+          <t>access_to_system_backups</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Access to system backups'}</t>
+          <t>Access to system backups</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'access_to_security_logs'}</t>
+          <t>access_to_security_logs</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Access to security logs'}</t>
+          <t>Access to security logs</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'access_to_system_configurations'}</t>
+          <t>access_to_system_configurations</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Access to system configurations'}</t>
+          <t>Access to system configurations</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1861,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'access_to_system_updates'}</t>
+          <t>access_to_system_updates</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Access to system updates'}</t>
+          <t>Access to system updates</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'access_to_all_systems'}</t>
+          <t>access_to_all_systems</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Access to all systems'}</t>
+          <t>Access to all systems</t>
         </is>
       </c>
     </row>
